--- a/questionnaire_templates/017_child_habit_tracker_setup_form--questionnaire_templates.xlsx
+++ b/questionnaire_templates/017_child_habit_tracker_setup_form--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -835,8 +835,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -864,12 +864,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'brushing_teeth_twice_daily',_'value':_'teeth'}</t>
+          <t>brushing_teeth_twice_daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Brushing Teeth Twice Daily', 'value': 'teeth'}</t>
+          <t>Brushing Teeth Twice Daily</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'tidying_room_and_toys',_'value':_'tidy'}</t>
+          <t>tidying_room_and_toys</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Tidying Room and Toys', 'value': 'tidy'}</t>
+          <t>Tidying Room and Toys</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'reading_for_20_minutes',_'value':_'reading'}</t>
+          <t>reading_for_20_minutes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Reading for 20 Minutes', 'value': 'reading'}</t>
+          <t>Reading for 20 Minutes</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'completing_homework_on_time',_'value':_'homework'}</t>
+          <t>completing_homework_on_time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Completing Homework on Time', 'value': 'homework'}</t>
+          <t>Completing Homework on Time</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'eating_all_vegetables',_'value':_'veggies'}</t>
+          <t>eating_all_vegetables</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Eating All Vegetables', 'value': 'veggies'}</t>
+          <t>Eating All Vegetables</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'daily_basis',_'value':_'daily'}</t>
+          <t>daily_basis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Daily Basis', 'value': 'daily'}</t>
+          <t>Daily Basis</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'weekdays_only',_'value':_'weekdays'}</t>
+          <t>weekdays_only</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Weekdays only', 'value': 'weekdays'}</t>
+          <t>Weekdays only</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'weekends_only',_'value':_'weekends'}</t>
+          <t>weekends_only</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Weekends only', 'value': 'weekends'}</t>
+          <t>Weekends only</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'sticker_chart',_'value':_'stickers'}</t>
+          <t>sticker_chart</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Sticker Chart', 'value': 'stickers'}</t>
+          <t>Sticker Chart</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'extra_screen_time',_'value':_'screen'}</t>
+          <t>extra_screen_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Extra Screen Time', 'value': 'screen'}</t>
+          <t>Extra Screen Time</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'small_toy_or_prize',_'value':_'toy'}</t>
+          <t>small_toy_or_prize</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Small Toy or Prize', 'value': 'toy'}</t>
+          <t>Small Toy or Prize</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'special_family_outing',_'value':_'outing'}</t>
+          <t>special_family_outing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Special Family Outing', 'value': 'outing'}</t>
+          <t>Special Family Outing</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_email_reminders',_'value':_true}</t>
+          <t>yes_-_email_reminders</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Email reminders', 'value': True}</t>
+          <t>Yes - Email reminders</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_i_will_track_manually',_'value':_false}</t>
+          <t>no_-_i_will_track_manually</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'No - I will track manually', 'value': False}</t>
+          <t>No - I will track manually</t>
         </is>
       </c>
     </row>
